--- a/testing/08_UAT_Plan_and_Test_Cases.xlsx
+++ b/testing/08_UAT_Plan_and_Test_Cases.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UAT Plan" sheetId="1" r:id="R4f99b869bd8c4e4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UAT Test Cases" sheetId="2" r:id="R99f21c6df5e54a6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UAT Plan" sheetId="1" r:id="R7c5af68ea5874c71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UAT Test Cases" sheetId="2" r:id="Rf96543f5a62d4b8a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -810,7 +810,7 @@
         <x:v>Validate requests vs dispositions trend</x:v>
       </x:c>
       <x:c r="C10" s="36" t="str">
-        <x:v>Confirm monthly intake and completion activity can be compared consistently.</x:v>
+        <x:v>Confirm monthly intake and disposition activity can be compared consistently.</x:v>
       </x:c>
       <x:c r="D10" s="36" t="str">
         <x:v>FR-06 / US-05</x:v>
@@ -931,10 +931,10 @@
         <x:v>UAT-09</x:v>
       </x:c>
       <x:c r="B14" s="36" t="str">
-        <x:v>Validate open vs completed distinction</x:v>
+        <x:v>Validate open vs dispositioned distinction</x:v>
       </x:c>
       <x:c r="C14" s="36" t="str">
-        <x:v>Confirm backlog metrics are not conflated with historical completed volume.</x:v>
+        <x:v>Confirm backlog metrics are not conflated with historical dispositioned volume.</x:v>
       </x:c>
       <x:c r="D14" s="36" t="str">
         <x:v>FR-11</x:v>
@@ -943,10 +943,10 @@
         <x:v>Open and closed/disposition data are present.</x:v>
       </x:c>
       <x:c r="F14" s="36" t="str">
-        <x:v>1) Compare backlog measures to open-record population. 2) Compare disposition measures to completed records. 3) Review definitions.</x:v>
+        <x:v>1) Compare backlog measures to open-record population. 2) Compare disposition measures to records that exited the workflow. 3) Review definitions.</x:v>
       </x:c>
       <x:c r="G14" s="36" t="str">
-        <x:v>Backlog measures use open records; disposition/completion measures use their documented completed-record logic.</x:v>
+        <x:v>Backlog measures use open records; disposition measures use their documented workflow-exit logic.</x:v>
       </x:c>
       <x:c r="H14" s="36" t="str">
         <x:v>Must</x:v>
@@ -1139,7 +1139,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9985b3840c30417d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5d612f4e42240b9"/>
   </x:tableParts>
 </x:worksheet>
 </file>